--- a/src/test/resources/TestDriver/TestRevenue/Test.xlsx
+++ b/src/test/resources/TestDriver/TestRevenue/Test.xlsx
@@ -42,7 +42,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">O_TransactionActivity5!$A$2:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">O_Attribute5!$A$2:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">O_Instrument5!$A$2:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">O_InstrumentAttribute!$A$2:$R$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">O_InstrumentAttribute!$A$2:$Q$12</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>Steps</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t>effectiveDate</t>
-  </si>
-  <si>
-    <t>batchId</t>
   </si>
   <si>
     <t>endDate</t>
@@ -576,7 +573,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -595,7 +592,6 @@
     <xf fontId="0" fillId="3" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyProtection="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyProtection="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1"/>
     <xf fontId="4" fillId="2" borderId="2" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5400,21 +5396,20 @@
     <col customWidth="1" min="1" max="1" style="1" width="21.7109375"/>
     <col customWidth="1" min="2" max="2" style="1" width="21.85546875"/>
     <col customWidth="1" min="3" max="3" style="1" width="24.140625"/>
-    <col customWidth="1" min="5" max="5" style="1" width="24.7109375"/>
-    <col customWidth="1" min="6" max="6" style="1" width="23.140625"/>
-    <col customWidth="1" min="8" max="8" style="1" width="7"/>
-    <col customWidth="1" min="9" max="9" style="1" width="20.42578125"/>
-    <col customWidth="1" min="10" max="10" style="1" width="21.140625"/>
-    <col customWidth="1" min="11" max="12" style="1" width="24.140625"/>
-    <col customWidth="1" min="13" max="13" style="1" width="19"/>
-    <col customWidth="1" min="14" max="14" style="1" width="31.5703125"/>
-    <col customWidth="1" min="15" max="15" style="1" width="16.7109375"/>
-    <col customWidth="1" min="16" max="16" style="1" width="26.28515625"/>
-    <col customWidth="1" min="17" max="17" style="1" width="21.7109375"/>
-    <col customWidth="1" min="18" max="18" style="1" width="30.42578125"/>
+    <col customWidth="1" min="5" max="5" style="1" width="23.140625"/>
+    <col customWidth="1" min="7" max="7" style="1" width="7"/>
+    <col customWidth="1" min="8" max="8" style="1" width="20.42578125"/>
+    <col customWidth="1" min="9" max="9" style="1" width="21.140625"/>
+    <col customWidth="1" min="10" max="11" style="1" width="24.140625"/>
+    <col customWidth="1" min="12" max="12" style="1" width="19"/>
+    <col customWidth="1" min="13" max="13" style="1" width="31.5703125"/>
+    <col customWidth="1" min="14" max="14" style="1" width="16.7109375"/>
+    <col customWidth="1" min="15" max="15" style="1" width="26.28515625"/>
+    <col customWidth="1" min="16" max="16" style="1" width="21.7109375"/>
+    <col customWidth="1" min="17" max="17" style="1" width="30.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="14.25">
       <c r="A1" s="4" t="s">
         <v>62</v>
       </c>
@@ -5474,9 +5469,6 @@
       <c r="Q2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
@@ -5486,37 +5478,34 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="E3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>81</v>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -5527,52 +5516,49 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="1">
+        <v>-200</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1">
+        <v>-200</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="1">
-        <v>-200</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="P4" s="1">
         <v>1</v>
       </c>
-      <c r="N4" s="1">
-        <v>-200</v>
-      </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
@@ -5583,52 +5569,49 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="1">
+        <v>100</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="1">
-        <v>100</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="1">
+        <v>12</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1200</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M5" s="1">
-        <v>12</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1200</v>
-      </c>
       <c r="O5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P5" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>2</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -5639,52 +5622,49 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="1">
+        <v>300</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="M6" s="1">
+        <v>300</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="1">
-        <v>300</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>300</v>
-      </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -5695,52 +5675,49 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="1">
+        <v>50</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J7" s="1">
-        <v>50</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="L7" s="1">
+        <v>12</v>
       </c>
       <c r="M7" s="1">
-        <v>12</v>
-      </c>
-      <c r="N7" s="1">
         <v>600</v>
       </c>
+      <c r="N7" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="O7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>5</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -5751,34 +5728,32 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>202201</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>81</v>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
@@ -5789,49 +5764,47 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
         <v>202201</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-200</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>-200</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" s="1">
         <v>1</v>
       </c>
-      <c r="N9" s="1">
-        <v>-200</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
@@ -5842,49 +5815,47 @@
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
         <v>202201</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="1">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="1">
-        <v>100</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="1">
+        <v>12</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1200</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="1">
-        <v>12</v>
-      </c>
-      <c r="N10" s="1">
-        <v>1200</v>
-      </c>
       <c r="O10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>2</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
@@ -5895,49 +5866,47 @@
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>202201</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="1">
+        <v>300</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>300</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
-        <v>202201</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="1">
-        <v>300</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
-        <v>300</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>3</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
@@ -5948,53 +5917,51 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="1">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
         <v>202201</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="1">
-        <v>50</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="L12" s="1">
+        <v>24</v>
       </c>
       <c r="M12" s="1">
-        <v>24</v>
-      </c>
-      <c r="N12" s="1">
         <v>1200</v>
       </c>
+      <c r="N12" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="O12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P12" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>5</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>90</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="A3:R12">
+  <sortState ref="A3:Q12">
     <sortCondition ref="A3:A12"/>
     <sortCondition ref="B3:B12"/>
     <sortCondition ref="D3:D12"/>
@@ -6029,50 +5996,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="21">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" ht="15">
+      <c r="A2" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row r="2" ht="15">
-      <c r="A2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="L2" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="O2" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="P2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="Q2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>96</v>
+      <c r="R2" s="19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="15">
@@ -6080,34 +6047,34 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18"/>
+      <c r="M3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N3" s="21">
-        <v>0</v>
-      </c>
-      <c r="O3" s="22">
+      <c r="N3" s="20">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21">
         <v>44620</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="21">
         <v>44620</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="22">
         <v>1900</v>
       </c>
     </row>
@@ -6116,32 +6083,32 @@
         <v>2</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="E4" s="8"/>
-      <c r="L4" s="19"/>
+      <c r="L4" s="18"/>
       <c r="M4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4" s="21">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22">
+        <v>105</v>
+      </c>
+      <c r="N4" s="20">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21">
         <v>44712</v>
       </c>
-      <c r="P4" s="22">
+      <c r="P4" s="21">
         <v>44712</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="22">
         <v>600</v>
       </c>
     </row>
@@ -6150,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="8"/>
     </row>
@@ -6165,13 +6132,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="8"/>
     </row>
@@ -6180,13 +6147,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="E7" s="8"/>
     </row>
@@ -6195,48 +6162,48 @@
         <v>0</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
     <row r="11" ht="21">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" ht="15">
+      <c r="A12" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-    </row>
-    <row r="12" ht="15">
-      <c r="A12" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="F12" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="H12" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="13" ht="15">
@@ -6247,25 +6214,25 @@
         <f t="shared" ref="B13:B16" si="0">IFERROR(VLOOKUP(A13,A3:$B$7,2,FALSE()),"")</f>
         <v>Discount</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>-200</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <f t="shared" ref="D13:D16" si="1">IFERROR(IF(VLOOKUP(B13,$B$3:$C$7,2,FALSE())="USE SALES PRICE",C13,VLOOKUP(B13,$B$3:$E$7,4,FALSE())),"")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <f t="shared" ref="E13:E16" si="2">IFERROR(D13/$D$18,"")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f t="shared" ref="F13:F16" si="3">IFERROR(E13*$C$18,"")</f>
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>44576</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>44576</v>
       </c>
     </row>
@@ -6277,25 +6244,25 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Basic Subscription</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>1200</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="24">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <f t="shared" si="3"/>
         <v>1085.7142857142856</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>44576</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>44941</v>
       </c>
     </row>
@@ -6307,25 +6274,25 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Implementation</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>300</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f t="shared" si="3"/>
         <v>271.42857142857139</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="21">
         <v>44576</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>44576</v>
       </c>
     </row>
@@ -6337,56 +6304,56 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Premium Subscription</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>600</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <f t="shared" si="3"/>
         <v>542.85714285714278</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>44576</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
     <row r="18" ht="15">
-      <c r="A18" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27">
+      <c r="A18" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26">
         <f>SUM(C13:C17)</f>
         <v>1900</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>SUM(D13:D17)</f>
         <v>2100</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <f>SUM(E13:E17)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <f>SUM(F13:F17)</f>
         <v>1899.9999999999995</v>
       </c>
@@ -6394,25 +6361,25 @@
       <c r="H18" s="8"/>
     </row>
     <row r="20">
-      <c r="B20" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="B20" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="D21" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="22">
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>44592</v>
       </c>
       <c r="C22" s="8">
@@ -6425,7 +6392,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>44620</v>
       </c>
       <c r="C23" s="8">
@@ -6438,7 +6405,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="30">
+      <c r="B24" s="29">
         <v>44651</v>
       </c>
       <c r="C24" s="8">
@@ -6451,7 +6418,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>44681</v>
       </c>
       <c r="C25" s="8">
@@ -6464,7 +6431,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>44712</v>
       </c>
       <c r="C26" s="8">
@@ -6477,7 +6444,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>44742</v>
       </c>
       <c r="C27" s="8">
@@ -6490,7 +6457,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>44773</v>
       </c>
       <c r="C28" s="8">
@@ -6503,7 +6470,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>44804</v>
       </c>
       <c r="C29" s="8">
@@ -6516,7 +6483,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>44834</v>
       </c>
       <c r="C30" s="8">
@@ -6529,7 +6496,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>44865</v>
       </c>
       <c r="C31" s="8">
@@ -6542,7 +6509,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>44895</v>
       </c>
       <c r="C32" s="8">
@@ -6555,7 +6522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>44926</v>
       </c>
       <c r="C33" s="8">
@@ -6568,7 +6535,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>44941</v>
       </c>
       <c r="C34" s="8">
@@ -6592,25 +6559,25 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
+      <c r="B38" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
     </row>
     <row r="39">
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="D39" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="29" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="40">
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>44592</v>
       </c>
       <c r="C40" s="8">
@@ -6623,7 +6590,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>44620</v>
       </c>
       <c r="C41" s="8">
@@ -6636,7 +6603,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="30">
+      <c r="B42" s="29">
         <v>44651</v>
       </c>
       <c r="C42" s="8">
@@ -6649,7 +6616,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="30">
+      <c r="B43" s="29">
         <v>44681</v>
       </c>
       <c r="C43" s="8">
@@ -6662,7 +6629,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="30">
+      <c r="B44" s="29">
         <v>44712</v>
       </c>
       <c r="C44" s="8">
@@ -6675,7 +6642,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="30">
+      <c r="B45" s="29">
         <v>44742</v>
       </c>
       <c r="C45" s="8">
@@ -6688,7 +6655,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="30">
+      <c r="B46" s="29">
         <v>44773</v>
       </c>
       <c r="C46" s="8">
@@ -6701,7 +6668,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="30">
+      <c r="B47" s="29">
         <v>44804</v>
       </c>
       <c r="C47" s="8">
@@ -6714,7 +6681,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="30">
+      <c r="B48" s="29">
         <v>44834</v>
       </c>
       <c r="C48" s="8">
@@ -6727,7 +6694,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="30">
+      <c r="B49" s="29">
         <v>44865</v>
       </c>
       <c r="C49" s="8">
@@ -6740,7 +6707,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="30">
+      <c r="B50" s="29">
         <v>44895</v>
       </c>
       <c r="C50" s="8">
@@ -6753,7 +6720,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="30">
+      <c r="B51" s="29">
         <v>44926</v>
       </c>
       <c r="C51" s="8">
@@ -6766,7 +6733,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="30">
+      <c r="B52" s="29">
         <v>44941</v>
       </c>
       <c r="C52" s="8">
@@ -6790,49 +6757,49 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
+      <c r="A55" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
     </row>
     <row r="57" ht="21">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+    </row>
+    <row r="58" ht="15">
+      <c r="A58" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-    </row>
-    <row r="58" ht="15">
-      <c r="A58" s="18" t="s">
+      <c r="B58" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="D58" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="E58" s="17" t="s">
         <v>95</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="59">
@@ -6840,13 +6807,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="D59" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E59" s="8">
         <v>0</v>
@@ -6857,13 +6824,13 @@
         <v>2</v>
       </c>
       <c r="B60" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="D60" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="E60" s="8"/>
     </row>
@@ -6872,13 +6839,13 @@
         <v>3</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E61" s="8"/>
     </row>
@@ -6887,13 +6854,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62" s="8"/>
     </row>
@@ -6902,13 +6869,13 @@
         <v>5</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="E63" s="8"/>
     </row>
@@ -6917,48 +6884,48 @@
         <v>0</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
     </row>
     <row r="67" ht="21">
-      <c r="A67" s="24" t="s">
+      <c r="A67" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+    </row>
+    <row r="68" ht="15">
+      <c r="A68" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-    </row>
-    <row r="68" ht="15">
-      <c r="A68" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="18" t="s">
+      <c r="D68" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="E68" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="F68" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F68" s="18" t="s">
+      <c r="G68" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G68" s="18" t="s">
+      <c r="H68" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="69" ht="15">
@@ -6969,25 +6936,25 @@
         <f t="shared" ref="B69:B72" si="8">IFERROR(VLOOKUP(A69,A$7:$B59,2,FALSE()),"")</f>
         <v>Discount</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="24">
         <v>-200</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="24">
         <f t="shared" ref="D69:D72" si="9">IFERROR(IF(VLOOKUP(B69,$B$3:$C$7,2,FALSE())="USE SALES PRICE",C69,VLOOKUP(B69,$B$3:$E$7,4,FALSE())),"")</f>
         <v>0</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="24">
         <f>IFERROR(D69/$D$18,"")</f>
         <v>0</v>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="24">
         <f>IFERROR(E69*$C$18,"")</f>
         <v>0</v>
       </c>
-      <c r="G69" s="22">
+      <c r="G69" s="21">
         <v>44576</v>
       </c>
-      <c r="H69" s="22">
+      <c r="H69" s="21">
         <v>44576</v>
       </c>
     </row>
@@ -6999,25 +6966,25 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Basic Subscription</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="24">
         <v>1200</v>
       </c>
-      <c r="D70" s="25">
+      <c r="D70" s="24">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="24">
         <f t="shared" ref="E70:E72" si="10">IFERROR(D70/$D$74,"")</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F70" s="25">
+      <c r="F70" s="24">
         <f t="shared" ref="F70:F72" si="11">IFERROR(E70*$C$74,"")</f>
         <v>1111.1111111111111</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G70" s="21">
         <v>44576</v>
       </c>
-      <c r="H70" s="22">
+      <c r="H70" s="21">
         <v>44941</v>
       </c>
     </row>
@@ -7029,25 +6996,25 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Implementation</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="24">
         <v>300</v>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="24">
         <f t="shared" si="9"/>
         <v>300</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="24">
         <f t="shared" si="10"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="24">
         <f t="shared" si="11"/>
         <v>277.77777777777777</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="21">
         <v>44576</v>
       </c>
-      <c r="H71" s="22">
+      <c r="H71" s="21">
         <v>44576</v>
       </c>
     </row>
@@ -7059,56 +7026,56 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Premium Subscription</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="24">
         <v>1200</v>
       </c>
-      <c r="D72" s="25">
+      <c r="D72" s="24">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="E72" s="25">
+      <c r="E72" s="24">
         <f t="shared" si="10"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F72" s="25">
+      <c r="F72" s="24">
         <f t="shared" si="11"/>
         <v>1111.1111111111111</v>
       </c>
-      <c r="G72" s="22">
+      <c r="G72" s="21">
         <v>44576</v>
       </c>
-      <c r="H72" s="22">
+      <c r="H72" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
     <row r="74" ht="15">
-      <c r="A74" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="27">
+      <c r="A74" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B74" s="25"/>
+      <c r="C74" s="26">
         <f>SUM(C69:C73)</f>
         <v>2500</v>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="26">
         <f>SUM(D69:D73)</f>
         <v>2700</v>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="26">
         <f>SUM(E69:E73)</f>
         <v>1</v>
       </c>
-      <c r="F74" s="27">
+      <c r="F74" s="26">
         <f>SUM(F69:F73)</f>
         <v>2500</v>
       </c>
@@ -7116,25 +7083,25 @@
       <c r="H74" s="8"/>
     </row>
     <row r="76">
-      <c r="B76" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
+      <c r="B76" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
     </row>
     <row r="77">
-      <c r="B77" s="29" t="s">
+      <c r="B77" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="D77" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="29" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="78">
-      <c r="B78" s="30">
+      <c r="B78" s="29">
         <v>44592</v>
       </c>
       <c r="C78" s="8">
@@ -7147,7 +7114,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="30">
+      <c r="B79" s="29">
         <v>44620</v>
       </c>
       <c r="C79" s="8">
@@ -7160,7 +7127,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="30">
+      <c r="B80" s="29">
         <v>44651</v>
       </c>
       <c r="C80" s="8">
@@ -7173,7 +7140,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="30">
+      <c r="B81" s="29">
         <v>44681</v>
       </c>
       <c r="C81" s="8">
@@ -7186,7 +7153,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="30">
+      <c r="B82" s="29">
         <v>44712</v>
       </c>
       <c r="C82" s="8">
@@ -7199,7 +7166,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="30">
+      <c r="B83" s="29">
         <v>44742</v>
       </c>
       <c r="C83" s="8">
@@ -7212,7 +7179,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="30">
+      <c r="B84" s="29">
         <v>44773</v>
       </c>
       <c r="C84" s="8">
@@ -7225,7 +7192,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="30">
+      <c r="B85" s="29">
         <v>44804</v>
       </c>
       <c r="C85" s="8">
@@ -7238,7 +7205,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="30">
+      <c r="B86" s="29">
         <v>44834</v>
       </c>
       <c r="C86" s="8">
@@ -7251,7 +7218,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="30">
+      <c r="B87" s="29">
         <v>44865</v>
       </c>
       <c r="C87" s="8">
@@ -7264,7 +7231,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="30">
+      <c r="B88" s="29">
         <v>44895</v>
       </c>
       <c r="C88" s="8">
@@ -7277,7 +7244,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="30">
+      <c r="B89" s="29">
         <v>44926</v>
       </c>
       <c r="C89" s="8">
@@ -7290,7 +7257,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="30">
+      <c r="B90" s="29">
         <v>44941</v>
       </c>
       <c r="C90" s="8">
@@ -7314,25 +7281,25 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C94" s="28"/>
-      <c r="D94" s="28"/>
+      <c r="B94" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
     </row>
     <row r="95">
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="D95" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="D95" s="29" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="96">
-      <c r="B96" s="30">
+      <c r="B96" s="29">
         <v>44592</v>
       </c>
       <c r="C96" s="8">
@@ -7345,7 +7312,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="30">
+      <c r="B97" s="29">
         <v>44620</v>
       </c>
       <c r="C97" s="8">
@@ -7358,7 +7325,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="30">
+      <c r="B98" s="29">
         <v>44651</v>
       </c>
       <c r="C98" s="8">
@@ -7371,7 +7338,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="30">
+      <c r="B99" s="29">
         <v>44681</v>
       </c>
       <c r="C99" s="8">
@@ -7384,7 +7351,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="30">
+      <c r="B100" s="29">
         <v>44712</v>
       </c>
       <c r="C100" s="8">
@@ -7397,7 +7364,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="30">
+      <c r="B101" s="29">
         <v>44742</v>
       </c>
       <c r="C101" s="8">
@@ -7410,7 +7377,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="30">
+      <c r="B102" s="29">
         <v>44773</v>
       </c>
       <c r="C102" s="8">
@@ -7423,7 +7390,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="30">
+      <c r="B103" s="29">
         <v>44804</v>
       </c>
       <c r="C103" s="8">
@@ -7436,7 +7403,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="30">
+      <c r="B104" s="29">
         <v>44834</v>
       </c>
       <c r="C104" s="8">
@@ -7449,7 +7416,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="30">
+      <c r="B105" s="29">
         <v>44865</v>
       </c>
       <c r="C105" s="8">
@@ -7462,7 +7429,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="30">
+      <c r="B106" s="29">
         <v>44895</v>
       </c>
       <c r="C106" s="8">
@@ -7475,7 +7442,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="30">
+      <c r="B107" s="29">
         <v>44926</v>
       </c>
       <c r="C107" s="8">
@@ -7488,7 +7455,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="30">
+      <c r="B108" s="29">
         <v>44941</v>
       </c>
       <c r="C108" s="8">
